--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2021_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2021_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:47</t>
+    <t xml:space="preserve">2026-09-09 22:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2021_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2021_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:34</t>
+    <t xml:space="preserve">2026-09-12 19:50</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2021_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2021_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:50</t>
+    <t xml:space="preserve">2026-09-24 00:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2021_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2021_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:29</t>
+    <t xml:space="preserve">2026-09-27 23:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -544,7 +544,7 @@
         <v>2021</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-0.22</v>
+        <v>-2.23</v>
       </c>
     </row>
     <row r="3">
@@ -561,7 +561,7 @@
         <v>2021</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-0.68</v>
+        <v>-6.82</v>
       </c>
     </row>
     <row r="4">
@@ -578,7 +578,7 @@
         <v>2021</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>-0.71</v>
+        <v>-7.12</v>
       </c>
     </row>
     <row r="5">
@@ -595,7 +595,7 @@
         <v>2021</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-0.94</v>
+        <v>-9.37</v>
       </c>
     </row>
     <row r="6">
@@ -612,7 +612,7 @@
         <v>2021</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-1.67</v>
+        <v>-16.65</v>
       </c>
     </row>
     <row r="7">
@@ -629,7 +629,7 @@
         <v>2021</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-1.73</v>
+        <v>-17.34</v>
       </c>
     </row>
     <row r="8">
@@ -646,7 +646,7 @@
         <v>2021</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-1.75</v>
+        <v>-17.54</v>
       </c>
     </row>
     <row r="9">
@@ -663,7 +663,7 @@
         <v>2021</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-2.02</v>
+        <v>-20.22</v>
       </c>
     </row>
     <row r="10">
@@ -680,7 +680,7 @@
         <v>2021</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-2.05</v>
+        <v>-20.51</v>
       </c>
     </row>
     <row r="11">
@@ -697,7 +697,7 @@
         <v>2021</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-2.56</v>
+        <v>-25.57</v>
       </c>
     </row>
     <row r="12">
@@ -714,7 +714,7 @@
         <v>2021</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>-2.63</v>
+        <v>-26.33</v>
       </c>
     </row>
     <row r="13">
@@ -731,7 +731,7 @@
         <v>2021</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>-2.79</v>
+        <v>-27.92</v>
       </c>
     </row>
     <row r="14">
@@ -748,7 +748,7 @@
         <v>2021</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>-3.07</v>
+        <v>-30.66</v>
       </c>
     </row>
     <row r="15">
@@ -765,7 +765,7 @@
         <v>2021</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-3.11</v>
+        <v>-31.12</v>
       </c>
     </row>
     <row r="16">
@@ -782,7 +782,7 @@
         <v>2021</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>-3.15</v>
+        <v>-31.53</v>
       </c>
     </row>
     <row r="17">
@@ -799,7 +799,7 @@
         <v>2021</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>-4.41</v>
+        <v>-44.08</v>
       </c>
     </row>
     <row r="18">
@@ -816,7 +816,7 @@
         <v>2021</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>-4.59</v>
+        <v>-45.88</v>
       </c>
     </row>
     <row r="19">
@@ -833,7 +833,7 @@
         <v>2021</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>-7.1</v>
+        <v>-71.04</v>
       </c>
     </row>
     <row r="20">
@@ -850,7 +850,7 @@
         <v>2021</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>-9.48</v>
+        <v>-94.82</v>
       </c>
     </row>
     <row r="21">
@@ -867,7 +867,7 @@
         <v>2021</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>-10.26</v>
+        <v>-102.6</v>
       </c>
     </row>
     <row r="22">
@@ -884,7 +884,7 @@
         <v>2021</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>-28.11</v>
+        <v>-281.14</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2021_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2021_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:11</t>
+    <t xml:space="preserve">2026-10-01 20:57</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2021_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2021_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:57</t>
+    <t xml:space="preserve">2026-10-02 13:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2021_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2021_nuble.xlsx
@@ -93,7 +93,7 @@
     <t xml:space="preserve">Treguaco</t>
   </si>
   <si>
-    <t xml:space="preserve">Ranquil</t>
+    <t xml:space="preserve">Ránquil</t>
   </si>
   <si>
     <t xml:space="preserve">Ñiquén</t>
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:34</t>
+    <t xml:space="preserve">2026-10-04 08:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2021_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2021_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:15</t>
+    <t xml:space="preserve">2026-10-05 08:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
